--- a/task133/target/arrears_roll_rates_fy26.xlsx
+++ b/task133/target/arrears_roll_rates_fy26.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="166925"/>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B97BE78-4DF6-4644-8F4A-03DD5205B868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{BBC4B652-E3A9-42A5-8BEC-843DCC17A9C7}"/>
+    <workbookView xWindow="1950" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{BBC4B652-E3A9-42A5-8BEC-843DCC17A9C7}"/>
   </bookViews>
   <sheets>
     <sheet name="Roll rates FY26" sheetId="1" r:id="rId1"/>
@@ -91,7 +91,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E5E9F0"/>
+        <fgColor rgb="FFE5E9F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -430,12 +430,12 @@
     <col min="6" max="6" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -465,19 +465,19 @@
         <v>45869</v>
       </c>
       <c r="B5" s="5">
-        <v>0.0245</v>
+        <v>0.0237</v>
       </c>
       <c r="C5" s="5">
-        <v>0.2987</v>
+        <v>0.3203</v>
       </c>
       <c r="D5" s="5">
-        <v>0.4372</v>
+        <v>0.4479</v>
       </c>
       <c r="E5" s="5">
-        <v>0.7612</v>
+        <v>0.7812</v>
       </c>
       <c r="F5" s="5">
-        <v>0.659</v>
+        <v>0.6322</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -485,19 +485,19 @@
         <v>45900</v>
       </c>
       <c r="B6" s="5">
-        <v>0.0247</v>
+        <v>0.0237</v>
       </c>
       <c r="C6" s="5">
-        <v>0.3124</v>
+        <v>0.3109</v>
       </c>
       <c r="D6" s="5">
-        <v>0.4428</v>
+        <v>0.4318</v>
       </c>
       <c r="E6" s="5">
-        <v>0.8519</v>
+        <v>0.7759</v>
       </c>
       <c r="F6" s="5">
-        <v>0.627</v>
+        <v>0.623</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -505,19 +505,19 @@
         <v>45930</v>
       </c>
       <c r="B7" s="5">
-        <v>0.0265</v>
+        <v>0.0264</v>
       </c>
       <c r="C7" s="5">
-        <v>0.2999</v>
+        <v>0.2896</v>
       </c>
       <c r="D7" s="5">
-        <v>0.4363</v>
+        <v>0.4006</v>
       </c>
       <c r="E7" s="5">
-        <v>0.6981</v>
+        <v>0.7469</v>
       </c>
       <c r="F7" s="5">
-        <v>0.6426</v>
+        <v>0.6602</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -525,19 +525,19 @@
         <v>45961</v>
       </c>
       <c r="B8" s="5">
-        <v>0.0222</v>
+        <v>0.0219</v>
       </c>
       <c r="C8" s="5">
-        <v>0.2805</v>
+        <v>0.2662</v>
       </c>
       <c r="D8" s="5">
-        <v>0.4719</v>
+        <v>0.4496</v>
       </c>
       <c r="E8" s="5">
-        <v>0.7532</v>
+        <v>0.777</v>
       </c>
       <c r="F8" s="5">
-        <v>0.6605</v>
+        <v>0.6691</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -545,19 +545,19 @@
         <v>45991</v>
       </c>
       <c r="B9" s="5">
-        <v>0.0282</v>
+        <v>0.0284</v>
       </c>
       <c r="C9" s="5">
-        <v>0.3466</v>
+        <v>0.3621</v>
       </c>
       <c r="D9" s="5">
-        <v>0.4527</v>
+        <v>0.41</v>
       </c>
       <c r="E9" s="5">
-        <v>0.7655</v>
+        <v>0.7985</v>
       </c>
       <c r="F9" s="5">
-        <v>0.5973</v>
+        <v>0.585</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -565,19 +565,19 @@
         <v>46022</v>
       </c>
       <c r="B10" s="5">
-        <v>0.0292</v>
+        <v>0.0276</v>
       </c>
       <c r="C10" s="5">
-        <v>0.2939</v>
+        <v>0.2879</v>
       </c>
       <c r="D10" s="5">
-        <v>0.3957</v>
+        <v>0.5151</v>
       </c>
       <c r="E10" s="5">
-        <v>0.7342</v>
+        <v>0.6835</v>
       </c>
       <c r="F10" s="5">
-        <v>0.6455</v>
+        <v>0.6576</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -585,19 +585,19 @@
         <v>46053</v>
       </c>
       <c r="B11" s="5">
-        <v>0.0353</v>
+        <v>0.0346</v>
       </c>
       <c r="C11" s="5">
-        <v>0.2676</v>
+        <v>0.2752</v>
       </c>
       <c r="D11" s="5">
-        <v>0.4307</v>
+        <v>0.3768</v>
       </c>
       <c r="E11" s="5">
-        <v>0.8182</v>
+        <v>0.7987</v>
       </c>
       <c r="F11" s="5">
-        <v>0.6539</v>
+        <v>0.6571</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -605,19 +605,19 @@
         <v>46081</v>
       </c>
       <c r="B12" s="5">
-        <v>0.0323</v>
+        <v>0.0308</v>
       </c>
       <c r="C12" s="5">
-        <v>0.3346</v>
+        <v>0.3151</v>
       </c>
       <c r="D12" s="5">
-        <v>0.4579</v>
+        <v>0.4915</v>
       </c>
       <c r="E12" s="5">
-        <v>0.6793</v>
+        <v>0.6725</v>
       </c>
       <c r="F12" s="5">
-        <v>0.6202</v>
+        <v>0.6287</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -625,19 +625,19 @@
         <v>46112</v>
       </c>
       <c r="B13" s="5">
-        <v>0.0258</v>
+        <v>0.0269</v>
       </c>
       <c r="C13" s="5">
-        <v>0.2577</v>
+        <v>0.2658</v>
       </c>
       <c r="D13" s="5">
-        <v>0.3604</v>
+        <v>0.3636</v>
       </c>
       <c r="E13" s="5">
-        <v>0.758</v>
+        <v>0.7143</v>
       </c>
       <c r="F13" s="5">
-        <v>0.6877</v>
+        <v>0.6726</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -645,19 +645,19 @@
         <v>46142</v>
       </c>
       <c r="B14" s="5">
-        <v>0.0255</v>
+        <v>0.0256</v>
       </c>
       <c r="C14" s="5">
-        <v>0.3272</v>
+        <v>0.3075</v>
       </c>
       <c r="D14" s="5">
-        <v>0.5224</v>
+        <v>0.4586</v>
       </c>
       <c r="E14" s="5">
-        <v>0.7188</v>
+        <v>0.7566</v>
       </c>
       <c r="F14" s="5">
-        <v>0.624</v>
+        <v>0.6398</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -665,19 +665,19 @@
         <v>46173</v>
       </c>
       <c r="B15" s="5">
-        <v>0.0248</v>
+        <v>0.0247</v>
       </c>
       <c r="C15" s="5">
-        <v>0.3086</v>
+        <v>0.3051</v>
       </c>
       <c r="D15" s="5">
-        <v>0.3882</v>
+        <v>0.4212</v>
       </c>
       <c r="E15" s="5">
-        <v>0.7423</v>
+        <v>0.7569</v>
       </c>
       <c r="F15" s="5">
-        <v>0.6181</v>
+        <v>0.6374</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -685,19 +685,19 @@
         <v>46203</v>
       </c>
       <c r="B16" s="5">
-        <v>0.0269</v>
+        <v>0.026</v>
       </c>
       <c r="C16" s="5">
-        <v>0.2976</v>
+        <v>0.2984</v>
       </c>
       <c r="D16" s="5">
-        <v>0.4077</v>
+        <v>0.4217</v>
       </c>
       <c r="E16" s="5">
-        <v>0.7315</v>
+        <v>0.7947</v>
       </c>
       <c r="F16" s="5">
-        <v>0.6457</v>
+        <v>0.6545</v>
       </c>
     </row>
   </sheetData>

--- a/task133/target/arrears_roll_rates_fy26.xlsx
+++ b/task133/target/arrears_roll_rates_fy26.xlsx
@@ -145,34 +145,34 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -180,9 +180,9 @@
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -209,14 +209,32 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -243,6 +261,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -254,166 +290,142 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 

--- a/task133/target/arrears_roll_rates_fy26.xlsx
+++ b/task133/target/arrears_roll_rates_fy26.xlsx
@@ -477,7 +477,7 @@
         <v>45869</v>
       </c>
       <c r="B5" s="5">
-        <v>0.0237</v>
+        <v>0.0238</v>
       </c>
       <c r="C5" s="5">
         <v>0.3203</v>
@@ -500,7 +500,7 @@
         <v>0.0237</v>
       </c>
       <c r="C6" s="5">
-        <v>0.3109</v>
+        <v>0.3117</v>
       </c>
       <c r="D6" s="5">
         <v>0.4318</v>
@@ -509,7 +509,7 @@
         <v>0.7759</v>
       </c>
       <c r="F6" s="5">
-        <v>0.623</v>
+        <v>0.6222</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -523,7 +523,7 @@
         <v>0.2896</v>
       </c>
       <c r="D7" s="5">
-        <v>0.4006</v>
+        <v>0.4023</v>
       </c>
       <c r="E7" s="5">
         <v>0.7469</v>
@@ -546,7 +546,7 @@
         <v>0.4496</v>
       </c>
       <c r="E8" s="5">
-        <v>0.777</v>
+        <v>0.7786</v>
       </c>
       <c r="F8" s="5">
         <v>0.6691</v>
@@ -563,7 +563,7 @@
         <v>0.3621</v>
       </c>
       <c r="D9" s="5">
-        <v>0.41</v>
+        <v>0.4118</v>
       </c>
       <c r="E9" s="5">
         <v>0.7985</v>
@@ -580,16 +580,16 @@
         <v>0.0276</v>
       </c>
       <c r="C10" s="5">
-        <v>0.2879</v>
+        <v>0.2872</v>
       </c>
       <c r="D10" s="5">
-        <v>0.5151</v>
+        <v>0.5117</v>
       </c>
       <c r="E10" s="5">
-        <v>0.6835</v>
+        <v>0.6857</v>
       </c>
       <c r="F10" s="5">
-        <v>0.6576</v>
+        <v>0.6582</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -600,13 +600,13 @@
         <v>0.0346</v>
       </c>
       <c r="C11" s="5">
-        <v>0.2752</v>
+        <v>0.2762</v>
       </c>
       <c r="D11" s="5">
-        <v>0.3768</v>
+        <v>0.3777</v>
       </c>
       <c r="E11" s="5">
-        <v>0.7987</v>
+        <v>0.7974</v>
       </c>
       <c r="F11" s="5">
         <v>0.6571</v>
@@ -617,16 +617,16 @@
         <v>46081</v>
       </c>
       <c r="B12" s="5">
-        <v>0.0308</v>
+        <v>0.0307</v>
       </c>
       <c r="C12" s="5">
         <v>0.3151</v>
       </c>
       <c r="D12" s="5">
-        <v>0.4915</v>
+        <v>0.4932</v>
       </c>
       <c r="E12" s="5">
-        <v>0.6725</v>
+        <v>0.6765</v>
       </c>
       <c r="F12" s="5">
         <v>0.6287</v>
@@ -640,16 +640,16 @@
         <v>0.0269</v>
       </c>
       <c r="C13" s="5">
-        <v>0.2658</v>
+        <v>0.2652</v>
       </c>
       <c r="D13" s="5">
         <v>0.3636</v>
       </c>
       <c r="E13" s="5">
-        <v>0.7143</v>
+        <v>0.7205</v>
       </c>
       <c r="F13" s="5">
-        <v>0.6726</v>
+        <v>0.6732</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -660,16 +660,16 @@
         <v>0.0256</v>
       </c>
       <c r="C14" s="5">
-        <v>0.3075</v>
+        <v>0.3081</v>
       </c>
       <c r="D14" s="5">
-        <v>0.4586</v>
+        <v>0.4601</v>
       </c>
       <c r="E14" s="5">
         <v>0.7566</v>
       </c>
       <c r="F14" s="5">
-        <v>0.6398</v>
+        <v>0.6392</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -683,7 +683,7 @@
         <v>0.3051</v>
       </c>
       <c r="D15" s="5">
-        <v>0.4212</v>
+        <v>0.4199</v>
       </c>
       <c r="E15" s="5">
         <v>0.7569</v>
@@ -703,7 +703,7 @@
         <v>0.2984</v>
       </c>
       <c r="D16" s="5">
-        <v>0.4217</v>
+        <v>0.4203</v>
       </c>
       <c r="E16" s="5">
         <v>0.7947</v>
